--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>VNRX</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -800,26 +807,26 @@
         <v>200</v>
       </c>
       <c r="F8" s="3">
+        <v>200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,91 +1134,97 @@
         <v>4400</v>
       </c>
       <c r="E12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G12" s="3">
         <v>5200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>4600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>3600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>4200</v>
       </c>
       <c r="M12" s="3">
         <v>3400</v>
       </c>
       <c r="N12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P12" s="3">
         <v>3600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>3200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>3700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>2600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>2300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>2300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>2900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>2500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>2300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>2400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>2700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1356,40 +1395,46 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1401,13 +1446,13 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L15" s="3">
         <v>300</v>
       </c>
       <c r="M15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>300</v>
@@ -1416,7 +1461,7 @@
         <v>300</v>
       </c>
       <c r="P15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q15" s="3">
         <v>300</v>
@@ -1431,7 +1476,7 @@
         <v>200</v>
       </c>
       <c r="U15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V15" s="3">
         <v>200</v>
@@ -1448,26 +1493,32 @@
       <c r="Z15" s="3">
         <v>200</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
+      <c r="AA15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>200</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F17" s="3">
         <v>8800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>8100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>8000</v>
       </c>
       <c r="I17" s="3">
         <v>8100</v>
       </c>
       <c r="J17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-9600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-9100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-8000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-8100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-7600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-6100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-4200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-4000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-4300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,55 +1780,57 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>800</v>
       </c>
       <c r="H20" s="3">
         <v>300</v>
       </c>
       <c r="I20" s="3">
+        <v>800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
@@ -1772,17 +1839,17 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1802,13 +1869,19 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,91 +1889,97 @@
         <v>-8100</v>
       </c>
       <c r="E21" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-9200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-8500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-7500</v>
       </c>
       <c r="J21" s="3">
         <v>-7500</v>
       </c>
       <c r="K21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="M21" s="3">
         <v>-7800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-6900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-5300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-3900</v>
       </c>
       <c r="V21" s="3">
         <v>-4000</v>
       </c>
       <c r="W21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="X21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-4100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1917,10 +1996,10 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1988,11 +2067,17 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-      <c r="AF22" s="3" t="s">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2000,91 +2085,97 @@
         <v>-8500</v>
       </c>
       <c r="E23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="G23" s="3">
         <v>-9600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3600</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-4200</v>
       </c>
       <c r="V23" s="3">
         <v>-4200</v>
       </c>
       <c r="W23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-4300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2364,14 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2276,91 +2379,97 @@
         <v>-8500</v>
       </c>
       <c r="E26" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="G26" s="3">
         <v>-9600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-4200</v>
       </c>
       <c r="V26" s="3">
         <v>-4200</v>
       </c>
       <c r="W26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-4300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2368,91 +2477,97 @@
         <v>-8400</v>
       </c>
       <c r="E27" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="G27" s="3">
         <v>-9500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-8800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-7200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-7600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-8000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-4200</v>
       </c>
       <c r="V27" s="3">
         <v>-4200</v>
       </c>
       <c r="W27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-4300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,55 +2952,61 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-800</v>
       </c>
       <c r="H32" s="3">
         <v>-300</v>
       </c>
       <c r="I32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
@@ -2876,17 +3015,17 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2906,13 +3045,19 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2920,91 +3065,97 @@
         <v>-8400</v>
       </c>
       <c r="E33" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="G33" s="3">
         <v>-9500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-8800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-7200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-7600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-8000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-4200</v>
       </c>
       <c r="V33" s="3">
         <v>-4200</v>
       </c>
       <c r="W33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-4300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3246,14 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3104,188 +3261,200 @@
         <v>-8400</v>
       </c>
       <c r="E35" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="G35" s="3">
         <v>-9500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-8800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-7200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-7600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-8000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-4200</v>
       </c>
       <c r="V35" s="3">
         <v>-4200</v>
       </c>
       <c r="W35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-4300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F41" s="3">
         <v>10800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>19700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>16400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>16700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>23700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>20600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>22900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>27900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>33100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>19400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>20900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>21300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>12000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>17000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>19700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>18500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>16200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>13400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>16400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>11900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>14300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>13800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>16500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>18500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>21700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,38 +3715,44 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>200</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -3586,8 +3771,8 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3595,8 +3780,8 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
@@ -3610,11 +3795,11 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,192 +3911,210 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>900</v>
+      </c>
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F46" s="3">
         <v>12200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>21500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>12200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>17700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>26000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>22000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>24400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>29400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>34700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>22200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>22400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>13100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>17600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>20300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>19200</v>
-      </c>
-      <c r="V46" s="3">
-        <v>17100</v>
-      </c>
-      <c r="W46" s="3">
-        <v>13900</v>
       </c>
       <c r="X46" s="3">
         <v>17100</v>
       </c>
       <c r="Y46" s="3">
+        <v>13900</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>17100</v>
+      </c>
+      <c r="AA46" s="3">
         <v>12500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>14900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>10600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>14300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>17000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>19000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>22000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,111 +4205,123 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F48" s="3">
         <v>5800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>6000</v>
       </c>
       <c r="G48" s="3">
         <v>6000</v>
       </c>
       <c r="H48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J48" s="3">
         <v>5500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3400</v>
-      </c>
-      <c r="T48" s="3">
-        <v>3100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>3200</v>
       </c>
       <c r="V48" s="3">
         <v>3100</v>
       </c>
       <c r="W48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X48" s="3">
         <v>3100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z48" s="3">
         <v>3200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>3300</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>3500</v>
       </c>
       <c r="AB48" s="3">
         <v>3500</v>
       </c>
       <c r="AC48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AE48" s="3">
         <v>3400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>3000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>2100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>100</v>
@@ -4109,10 +4330,10 @@
         <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K49" s="3">
         <v>200</v>
@@ -4121,10 +4342,10 @@
         <v>200</v>
       </c>
       <c r="M49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
@@ -4139,10 +4360,10 @@
         <v>300</v>
       </c>
       <c r="S49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U49" s="3">
         <v>400</v>
@@ -4151,19 +4372,19 @@
         <v>400</v>
       </c>
       <c r="W49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y49" s="3">
         <v>500</v>
       </c>
       <c r="Z49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AA49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB49" s="3">
         <v>600</v>
@@ -4178,10 +4399,16 @@
         <v>600</v>
       </c>
       <c r="AF49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH49" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>18000</v>
+        <v>19400</v>
       </c>
       <c r="E54" s="3">
-        <v>27600</v>
+        <v>28000</v>
       </c>
       <c r="F54" s="3">
         <v>18000</v>
       </c>
       <c r="G54" s="3">
+        <v>27600</v>
+      </c>
+      <c r="H54" s="3">
+        <v>18000</v>
+      </c>
+      <c r="I54" s="3">
         <v>18300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>23300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>24300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>31700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>27500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>30000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>35200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>40500</v>
-      </c>
-      <c r="O54" s="3">
-        <v>26200</v>
-      </c>
-      <c r="P54" s="3">
-        <v>26100</v>
       </c>
       <c r="Q54" s="3">
         <v>26200</v>
       </c>
       <c r="R54" s="3">
+        <v>26100</v>
+      </c>
+      <c r="S54" s="3">
+        <v>26200</v>
+      </c>
+      <c r="T54" s="3">
         <v>16900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>21300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>23800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>22900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>20600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>17500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>20700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>16300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>19000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>14600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>18400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>21000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>22500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>24700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,82 +4967,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>400</v>
       </c>
       <c r="AB57" s="3">
         <v>400</v>
@@ -4792,63 +5053,69 @@
         <v>400</v>
       </c>
       <c r="AD57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF57" s="3">
         <v>600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
         <v>1300</v>
       </c>
       <c r="F58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H58" s="3">
         <v>1200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1100</v>
       </c>
       <c r="I58" s="3">
         <v>1200</v>
       </c>
       <c r="J58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L58" s="3">
         <v>1400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>800</v>
       </c>
       <c r="M58" s="3">
         <v>900</v>
       </c>
       <c r="N58" s="3">
+        <v>800</v>
+      </c>
+      <c r="O58" s="3">
+        <v>900</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>900</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>800</v>
-      </c>
-      <c r="R58" s="3">
-        <v>700</v>
       </c>
       <c r="S58" s="3">
         <v>800</v>
@@ -4863,342 +5130,366 @@
         <v>700</v>
       </c>
       <c r="W58" s="3">
+        <v>800</v>
+      </c>
+      <c r="X58" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y58" s="3">
         <v>600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>27300</v>
+      </c>
+      <c r="F59" s="3">
         <v>13200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>14000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>13000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>13200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>13900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1800</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>1400</v>
       </c>
       <c r="AE59" s="3">
         <v>1600</v>
       </c>
       <c r="AF59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AH59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>31800</v>
+      </c>
+      <c r="F60" s="3">
         <v>17700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>18800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>17200</v>
-      </c>
-      <c r="G60" s="3">
-        <v>17400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>17000</v>
       </c>
       <c r="I60" s="3">
         <v>17400</v>
       </c>
       <c r="J60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K60" s="3">
+        <v>17400</v>
+      </c>
+      <c r="L60" s="3">
         <v>17500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3500</v>
-      </c>
-      <c r="V60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="W60" s="3">
-        <v>2300</v>
       </c>
       <c r="X60" s="3">
         <v>2700</v>
       </c>
       <c r="Y60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AA60" s="3">
         <v>3300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F61" s="3">
         <v>2900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>3000</v>
       </c>
       <c r="L61" s="3">
         <v>2800</v>
       </c>
       <c r="M61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O61" s="3">
         <v>3100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>400</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>400</v>
       </c>
       <c r="H62" s="3">
         <v>400</v>
       </c>
       <c r="I62" s="3">
+        <v>400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
@@ -5213,7 +5504,7 @@
         <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -5230,11 +5521,11 @@
       <c r="V62" s="3">
         <v>100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
+      <c r="W62" s="3">
+        <v>100</v>
+      </c>
+      <c r="X62" s="3">
+        <v>100</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
@@ -5242,11 +5533,11 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>35800</v>
+      </c>
+      <c r="F66" s="3">
         <v>20100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>21700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>20400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>20900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>20000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>19900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>9500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>7100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>7600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>7100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>6000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>6500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>5600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>6200</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>4700</v>
       </c>
       <c r="AB66" s="3">
         <v>5000</v>
       </c>
       <c r="AC66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AE66" s="3">
         <v>4400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>4000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>3600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-210900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-202600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-193900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-185500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-176000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-167300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-160000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-152300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-144600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-137000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-129000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-121800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-116300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-110200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-105000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-100700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-95700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-89800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-86300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-82100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-77900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-73700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-69400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-65000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-55700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-51700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-40900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-2000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-2300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-2600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>17900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>21300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>26700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>31200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>16300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>19000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>18700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>9200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>14200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>17800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>16400</v>
-      </c>
-      <c r="V76" s="3">
-        <v>15100</v>
-      </c>
-      <c r="W76" s="3">
-        <v>12100</v>
       </c>
       <c r="X76" s="3">
         <v>15100</v>
       </c>
       <c r="Y76" s="3">
-        <v>10000</v>
+        <v>12100</v>
       </c>
       <c r="Z76" s="3">
-        <v>14000</v>
+        <v>15100</v>
       </c>
       <c r="AA76" s="3">
         <v>10000</v>
       </c>
       <c r="AB76" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC76" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AD76" s="3">
         <v>13400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>16600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>18500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>21200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6959,117 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6688,91 +7077,97 @@
         <v>-8400</v>
       </c>
       <c r="E81" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="G81" s="3">
         <v>-9500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-8800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-7200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-7600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-8000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-4200</v>
       </c>
       <c r="V81" s="3">
         <v>-4200</v>
       </c>
       <c r="W81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-4300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6820,10 +7217,10 @@
         <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -6856,13 +7253,13 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -6883,10 +7280,10 @@
         <v>200</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-8400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-8700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-6200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-4400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-4800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-2800</v>
       </c>
       <c r="V89" s="3">
         <v>-3700</v>
       </c>
       <c r="W89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="X89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-3600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,64 +7922,66 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-300</v>
       </c>
       <c r="F91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
@@ -7564,19 +8005,25 @@
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,64 +8212,70 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>-300</v>
       </c>
       <c r="F94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-100</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
       </c>
       <c r="M94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
@@ -7840,19 +8299,25 @@
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,165 +8738,177 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>17300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>8100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>6700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>20200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>4600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>14100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>4600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>5200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>6600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>9100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>7700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>200</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>1100</v>
       </c>
       <c r="AD100" s="3">
         <v>300</v>
       </c>
       <c r="AE100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG100" s="3">
         <v>11900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
-      </c>
-      <c r="W101" s="3">
-        <v>200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>200</v>
@@ -8420,113 +8917,125 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-8900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>9700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>13600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>9300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-5000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>4500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>4100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>9200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>VNRX</t>
   </si>
@@ -656,152 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3">
         <v>200</v>
@@ -813,23 +817,23 @@
         <v>200</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E12" s="3">
         <v>4400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3400</v>
       </c>
       <c r="M12" s="3">
         <v>3400</v>
       </c>
       <c r="N12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O12" s="3">
         <v>4200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2500</v>
-      </c>
-      <c r="W12" s="3">
-        <v>2300</v>
       </c>
       <c r="X12" s="3">
         <v>2300</v>
       </c>
       <c r="Y12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Z12" s="3">
         <v>2900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1401,8 +1421,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
@@ -1410,8 +1430,8 @@
       <c r="AE14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1428,7 +1451,7 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
@@ -1437,7 +1460,7 @@
         <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1452,10 +1475,10 @@
         <v>300</v>
       </c>
       <c r="M15" s="3">
+        <v>300</v>
+      </c>
+      <c r="N15" s="3">
         <v>200</v>
-      </c>
-      <c r="N15" s="3">
-        <v>300</v>
       </c>
       <c r="O15" s="3">
         <v>300</v>
@@ -1467,19 +1490,19 @@
         <v>300</v>
       </c>
       <c r="R15" s="3">
+        <v>300</v>
+      </c>
+      <c r="S15" s="3">
         <v>200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>300</v>
-      </c>
-      <c r="V15" s="3">
-        <v>200</v>
       </c>
       <c r="W15" s="3">
         <v>200</v>
@@ -1499,8 +1522,8 @@
       <c r="AB15" s="3">
         <v>200</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
+      <c r="AC15" s="3">
+        <v>200</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>4</v>
@@ -1508,8 +1531,8 @@
       <c r="AE15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E17" s="3">
         <v>8600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3700</v>
-      </c>
-      <c r="V17" s="3">
-        <v>4200</v>
       </c>
       <c r="W17" s="3">
         <v>4200</v>
       </c>
       <c r="X17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Y17" s="3">
         <v>4000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4400</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>4600</v>
       </c>
       <c r="AB17" s="3">
         <v>4600</v>
       </c>
       <c r="AC17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AD17" s="3">
         <v>4000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>3500</v>
       </c>
       <c r="AH17" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-8000</v>
       </c>
       <c r="J18" s="3">
         <v>-8000</v>
       </c>
       <c r="K18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L18" s="3">
         <v>-8100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3700</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-4200</v>
       </c>
       <c r="W18" s="3">
         <v>-4200</v>
       </c>
       <c r="X18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-4600</v>
       </c>
       <c r="AB18" s="3">
         <v>-4600</v>
       </c>
       <c r="AC18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-3500</v>
       </c>
       <c r="AH18" s="3">
         <v>-3500</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>-3500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1794,65 +1828,65 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>400</v>
       </c>
       <c r="O20" s="3">
         <v>400</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1875,36 +1909,39 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7500</v>
       </c>
       <c r="K21" s="3">
         <v>-7500</v>
@@ -1913,73 +1950,76 @@
         <v>-7500</v>
       </c>
       <c r="M21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="N21" s="3">
         <v>-7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2002,7 +2042,7 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2073,70 +2113,73 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-      <c r="AH22" s="3" t="s">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-7700</v>
       </c>
       <c r="L23" s="3">
         <v>-7700</v>
       </c>
       <c r="M23" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="N23" s="3">
         <v>-8100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-4200</v>
       </c>
       <c r="W23" s="3">
         <v>-4200</v>
@@ -2145,37 +2188,40 @@
         <v>-4200</v>
       </c>
       <c r="Y23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,67 +2419,70 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-7700</v>
       </c>
       <c r="L26" s="3">
         <v>-7700</v>
       </c>
       <c r="M26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="N26" s="3">
         <v>-8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-4200</v>
       </c>
       <c r="W26" s="3">
         <v>-4200</v>
@@ -2439,96 +2491,99 @@
         <v>-4200</v>
       </c>
       <c r="Y26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-7600</v>
       </c>
       <c r="L27" s="3">
         <v>-7600</v>
       </c>
       <c r="M27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="N27" s="3">
         <v>-8000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-4200</v>
       </c>
       <c r="W27" s="3">
         <v>-4200</v>
@@ -2537,37 +2592,40 @@
         <v>-4200</v>
       </c>
       <c r="Y27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2970,65 +3040,65 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-400</v>
       </c>
       <c r="O32" s="3">
         <v>-400</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -3051,72 +3121,75 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-7600</v>
       </c>
       <c r="L33" s="3">
         <v>-7600</v>
       </c>
       <c r="M33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="N33" s="3">
         <v>-8000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-4200</v>
       </c>
       <c r="W33" s="3">
         <v>-4200</v>
@@ -3125,37 +3198,40 @@
         <v>-4200</v>
       </c>
       <c r="Y33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,67 +3328,70 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-7600</v>
       </c>
       <c r="L35" s="3">
         <v>-7600</v>
       </c>
       <c r="M35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="N35" s="3">
         <v>-8000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-4200</v>
       </c>
       <c r="W35" s="3">
         <v>-4200</v>
@@ -3321,140 +3400,146 @@
         <v>-4200</v>
       </c>
       <c r="Y35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>33100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>17000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>18500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>16500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>18500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,41 +3811,44 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>100</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -3777,14 +3870,14 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
@@ -3801,8 +3894,8 @@
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1500</v>
       </c>
       <c r="O45" s="3">
         <v>1500</v>
       </c>
       <c r="P45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1200</v>
-      </c>
-      <c r="S45" s="3">
-        <v>1100</v>
       </c>
       <c r="T45" s="3">
         <v>1100</v>
       </c>
       <c r="U45" s="3">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="V45" s="3">
         <v>600</v>
       </c>
       <c r="W45" s="3">
+        <v>600</v>
+      </c>
+      <c r="X45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>600</v>
       </c>
       <c r="AB45" s="3">
         <v>600</v>
       </c>
       <c r="AC45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD45" s="3">
         <v>500</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>400</v>
       </c>
       <c r="AE45" s="3">
         <v>400</v>
       </c>
       <c r="AF45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG45" s="3">
         <v>500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E46" s="3">
         <v>13500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>26000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>19000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>22000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,22 +4316,25 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6000</v>
       </c>
       <c r="H48" s="3">
         <v>6000</v>
@@ -4235,61 +4343,61 @@
         <v>6000</v>
       </c>
       <c r="J48" s="3">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="K48" s="3">
         <v>5500</v>
       </c>
       <c r="L48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="M48" s="3">
         <v>5600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5300</v>
       </c>
       <c r="N48" s="3">
         <v>5300</v>
       </c>
       <c r="O48" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="P48" s="3">
         <v>5600</v>
       </c>
       <c r="Q48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="R48" s="3">
         <v>5500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3500</v>
-      </c>
-      <c r="T48" s="3">
-        <v>3400</v>
       </c>
       <c r="U48" s="3">
         <v>3400</v>
       </c>
       <c r="V48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W48" s="3">
         <v>3100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3200</v>
-      </c>
-      <c r="X48" s="3">
-        <v>3100</v>
       </c>
       <c r="Y48" s="3">
         <v>3100</v>
       </c>
       <c r="Z48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA48" s="3">
         <v>3200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3300</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>3500</v>
       </c>
       <c r="AC48" s="3">
         <v>3500</v>
@@ -4298,33 +4406,36 @@
         <v>3500</v>
       </c>
       <c r="AE48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AF48" s="3">
         <v>3400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>300</v>
+      </c>
+      <c r="E49" s="3">
         <v>200</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>100</v>
@@ -4336,7 +4447,7 @@
         <v>100</v>
       </c>
       <c r="K49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L49" s="3">
         <v>200</v>
@@ -4348,7 +4459,7 @@
         <v>200</v>
       </c>
       <c r="O49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P49" s="3">
         <v>300</v>
@@ -4366,7 +4477,7 @@
         <v>300</v>
       </c>
       <c r="U49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V49" s="3">
         <v>400</v>
@@ -4378,7 +4489,7 @@
         <v>400</v>
       </c>
       <c r="Y49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z49" s="3">
         <v>500</v>
@@ -4387,7 +4498,7 @@
         <v>500</v>
       </c>
       <c r="AB49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AC49" s="3">
         <v>600</v>
@@ -4405,10 +4516,13 @@
         <v>600</v>
       </c>
       <c r="AH49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI49" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E54" s="3">
         <v>19400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>28000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>20600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>20700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>14600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>21000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>24700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,85 +5099,86 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3000</v>
       </c>
       <c r="I57" s="3">
         <v>3000</v>
       </c>
       <c r="J57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1500</v>
       </c>
       <c r="Q57" s="3">
         <v>1500</v>
       </c>
       <c r="R57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>400</v>
       </c>
       <c r="AC57" s="3">
         <v>400</v>
@@ -5059,408 +5190,423 @@
         <v>400</v>
       </c>
       <c r="AF57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG57" s="3">
         <v>600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E58" s="3">
         <v>1300</v>
       </c>
       <c r="F58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1200</v>
       </c>
       <c r="I58" s="3">
         <v>1200</v>
       </c>
       <c r="J58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1000</v>
       </c>
       <c r="Q58" s="3">
         <v>1000</v>
       </c>
       <c r="R58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S58" s="3">
         <v>900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>600</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>500</v>
       </c>
       <c r="AA58" s="3">
         <v>500</v>
       </c>
       <c r="AB58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC58" s="3">
         <v>700</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>600</v>
       </c>
       <c r="AD58" s="3">
         <v>600</v>
       </c>
       <c r="AE58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF58" s="3">
         <v>300</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>200</v>
       </c>
       <c r="AG58" s="3">
         <v>200</v>
       </c>
       <c r="AH58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E59" s="3">
         <v>26700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2500</v>
-      </c>
-      <c r="T59" s="3">
-        <v>2400</v>
       </c>
       <c r="U59" s="3">
         <v>2400</v>
       </c>
       <c r="V59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="W59" s="3">
         <v>2000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1400</v>
       </c>
       <c r="X59" s="3">
         <v>1400</v>
       </c>
       <c r="Y59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z59" s="3">
         <v>900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E60" s="3">
         <v>31500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>2000</v>
       </c>
       <c r="AH60" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E61" s="3">
         <v>4200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>2900</v>
       </c>
       <c r="AA61" s="3">
         <v>2900</v>
       </c>
       <c r="AB61" s="3">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="AC61" s="3">
         <v>2400</v>
       </c>
       <c r="AD61" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="AE61" s="3">
         <v>2100</v>
       </c>
       <c r="AF61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AG61" s="3">
         <v>1800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5471,13 +5617,13 @@
         <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
       </c>
       <c r="H62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I62" s="3">
         <v>400</v>
@@ -5486,28 +5632,28 @@
         <v>400</v>
       </c>
       <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>200</v>
-      </c>
-      <c r="R62" s="3">
-        <v>100</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -5527,8 +5673,8 @@
       <c r="X62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
+      <c r="Y62" s="3">
+        <v>100</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
@@ -5539,8 +5685,8 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E66" s="3">
         <v>35000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-217900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-210900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-202600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-193900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-185500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-176000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-167300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-160000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-152300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-144600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-137000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-129000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-121800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-116300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-110200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-105000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-95700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-86300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-82100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-77900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-73700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-69400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-55700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-51700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-40900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-15600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-7800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-2600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,170 +7154,176 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-7600</v>
       </c>
       <c r="L81" s="3">
         <v>-7600</v>
       </c>
       <c r="M81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="N81" s="3">
         <v>-8000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-4200</v>
       </c>
       <c r="W81" s="3">
         <v>-4200</v>
@@ -7137,37 +7332,40 @@
         <v>-4200</v>
       </c>
       <c r="Y81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7223,7 +7422,7 @@
         <v>300</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -7259,10 +7458,10 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>100</v>
-      </c>
-      <c r="V83" s="3">
-        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -7286,7 +7485,7 @@
         <v>200</v>
       </c>
       <c r="AD83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE83" s="3">
         <v>100</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-2800</v>
       </c>
       <c r="AE89" s="3">
         <v>-2800</v>
       </c>
       <c r="AF89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,16 +8144,17 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-300</v>
       </c>
       <c r="F91" s="3">
         <v>-300</v>
@@ -7942,19 +8163,19 @@
         <v>-300</v>
       </c>
       <c r="H91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -7963,28 +8184,28 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-300</v>
       </c>
       <c r="T91" s="3">
         <v>-300</v>
       </c>
       <c r="U91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
@@ -8011,19 +8232,22 @@
         <v>-100</v>
       </c>
       <c r="AE91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,16 +8445,19 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-300</v>
       </c>
       <c r="F94" s="3">
         <v>-300</v>
@@ -8236,19 +8466,19 @@
         <v>-300</v>
       </c>
       <c r="H94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
@@ -8257,28 +8487,28 @@
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="T94" s="3">
         <v>-300</v>
       </c>
       <c r="U94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V94" s="3">
         <v>-200</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-100</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
@@ -8305,19 +8535,22 @@
         <v>-100</v>
       </c>
       <c r="AE94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-300</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,115 +8987,121 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>20200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>14100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>7700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>11900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
@@ -8860,68 +9109,68 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -8929,113 +9178,119 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>VNRX</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>200</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
@@ -820,23 +824,23 @@
         <v>200</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
@@ -900,8 +904,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,31 +1008,34 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="E12" s="3">
-        <v>4400</v>
+        <v>3700</v>
       </c>
       <c r="F12" s="3">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="G12" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="H12" s="3">
-        <v>5200</v>
+        <v>4700</v>
       </c>
       <c r="I12" s="3">
-        <v>4600</v>
+        <v>5500</v>
       </c>
       <c r="J12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K12" s="3">
         <v>3600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3400</v>
       </c>
       <c r="N12" s="3">
         <v>3400</v>
       </c>
       <c r="O12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P12" s="3">
         <v>4200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2500</v>
-      </c>
-      <c r="X12" s="3">
-        <v>2300</v>
       </c>
       <c r="Y12" s="3">
         <v>2300</v>
       </c>
       <c r="Z12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>2900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,8 +1372,8 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1361,11 +1381,11 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1424,8 +1444,8 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>4</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>4</v>
@@ -1433,8 +1453,8 @@
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1454,13 +1477,13 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1478,10 +1501,10 @@
         <v>300</v>
       </c>
       <c r="N15" s="3">
+        <v>300</v>
+      </c>
+      <c r="O15" s="3">
         <v>200</v>
-      </c>
-      <c r="O15" s="3">
-        <v>300</v>
       </c>
       <c r="P15" s="3">
         <v>300</v>
@@ -1493,19 +1516,19 @@
         <v>300</v>
       </c>
       <c r="S15" s="3">
+        <v>300</v>
+      </c>
+      <c r="T15" s="3">
         <v>200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>300</v>
-      </c>
-      <c r="W15" s="3">
-        <v>200</v>
       </c>
       <c r="X15" s="3">
         <v>200</v>
@@ -1525,8 +1548,8 @@
       <c r="AC15" s="3">
         <v>200</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
+      <c r="AD15" s="3">
+        <v>200</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>4</v>
@@ -1534,8 +1557,8 @@
       <c r="AF15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3700</v>
-      </c>
-      <c r="W17" s="3">
-        <v>4200</v>
       </c>
       <c r="X17" s="3">
         <v>4200</v>
       </c>
       <c r="Y17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z17" s="3">
         <v>4000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4400</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>4600</v>
       </c>
       <c r="AC17" s="3">
         <v>4600</v>
       </c>
       <c r="AD17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AE17" s="3">
         <v>4000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AH17" s="3">
-        <v>3500</v>
       </c>
       <c r="AI17" s="3">
         <v>3500</v>
       </c>
+      <c r="AJ17" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-8800</v>
-      </c>
       <c r="G18" s="3">
-        <v>-8600</v>
+        <v>-8700</v>
       </c>
       <c r="H18" s="3">
-        <v>-9600</v>
+        <v>-8700</v>
       </c>
       <c r="I18" s="3">
-        <v>-9100</v>
+        <v>-9500</v>
       </c>
       <c r="J18" s="3">
-        <v>-8000</v>
+        <v>-9000</v>
       </c>
       <c r="K18" s="3">
         <v>-8000</v>
       </c>
       <c r="L18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="M18" s="3">
         <v>-8100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3700</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-4200</v>
       </c>
       <c r="X18" s="3">
         <v>-4200</v>
       </c>
       <c r="Y18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-4600</v>
       </c>
       <c r="AC18" s="3">
         <v>-4600</v>
       </c>
       <c r="AD18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>-3500</v>
       </c>
       <c r="AI18" s="3">
         <v>-3500</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>-3500</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,13 +1849,14 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1831,65 +1865,65 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>800</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>800</v>
-      </c>
-      <c r="K20" s="3">
-        <v>300</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>400</v>
       </c>
       <c r="P20" s="3">
         <v>400</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>500</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1912,39 +1946,42 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-8400</v>
-      </c>
       <c r="G21" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H21" s="3">
         <v>-8100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9200</v>
       </c>
-      <c r="I21" s="3">
-        <v>-8500</v>
-      </c>
       <c r="J21" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-7000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-7500</v>
       </c>
       <c r="L21" s="3">
         <v>-7500</v>
@@ -1953,73 +1990,76 @@
         <v>-7500</v>
       </c>
       <c r="N21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="O21" s="3">
         <v>-7800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2045,7 +2085,7 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2116,73 +2156,76 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-7700</v>
       </c>
       <c r="M23" s="3">
         <v>-7700</v>
       </c>
       <c r="N23" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="O23" s="3">
         <v>-8100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3600</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-4200</v>
       </c>
       <c r="X23" s="3">
         <v>-4200</v>
@@ -2191,60 +2234,63 @@
         <v>-4200</v>
       </c>
       <c r="Z23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,70 +2471,73 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-7700</v>
       </c>
       <c r="M26" s="3">
         <v>-7700</v>
       </c>
       <c r="N26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="O26" s="3">
         <v>-8100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-4200</v>
       </c>
       <c r="X26" s="3">
         <v>-4200</v>
@@ -2494,99 +2546,102 @@
         <v>-4200</v>
       </c>
       <c r="Z26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7700</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-7600</v>
       </c>
       <c r="M27" s="3">
         <v>-7600</v>
       </c>
       <c r="N27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="O27" s="3">
         <v>-8000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-4200</v>
       </c>
       <c r="X27" s="3">
         <v>-4200</v>
@@ -2595,37 +2650,40 @@
         <v>-4200</v>
       </c>
       <c r="Z27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,13 +3095,16 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -3043,65 +3113,65 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-400</v>
       </c>
       <c r="P32" s="3">
         <v>-400</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-500</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -3124,75 +3194,78 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7700</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-7600</v>
       </c>
       <c r="M33" s="3">
         <v>-7600</v>
       </c>
       <c r="N33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="O33" s="3">
         <v>-8000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-4200</v>
       </c>
       <c r="X33" s="3">
         <v>-4200</v>
@@ -3201,37 +3274,40 @@
         <v>-4200</v>
       </c>
       <c r="Z33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,70 +3407,73 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7700</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-7600</v>
       </c>
       <c r="M35" s="3">
         <v>-7600</v>
       </c>
       <c r="N35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="O35" s="3">
         <v>-8000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-4200</v>
       </c>
       <c r="X35" s="3">
         <v>-4200</v>
@@ -3403,143 +3482,149 @@
         <v>-4200</v>
       </c>
       <c r="Z35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E41" s="3">
         <v>6000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>33100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>18500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>14300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>18500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>21700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,44 +3904,47 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>100</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
@@ -3873,14 +3966,14 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
@@ -3897,8 +3990,8 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,233 +4112,242 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
+        <v>500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
+        <v>500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>700</v>
+      </c>
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="E45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>900</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="L45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O45" s="3">
         <v>1400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1500</v>
       </c>
       <c r="P45" s="3">
         <v>1500</v>
       </c>
       <c r="Q45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1100</v>
       </c>
       <c r="U45" s="3">
         <v>1100</v>
       </c>
       <c r="V45" s="3">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="W45" s="3">
         <v>600</v>
       </c>
       <c r="X45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y45" s="3">
         <v>700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>600</v>
       </c>
       <c r="AC45" s="3">
         <v>600</v>
       </c>
       <c r="AD45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE45" s="3">
         <v>500</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>400</v>
       </c>
       <c r="AF45" s="3">
         <v>400</v>
       </c>
       <c r="AG45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH45" s="3">
         <v>500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>26000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>22400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>19000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>22000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,25 +4424,28 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E48" s="3">
         <v>5400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6000</v>
       </c>
       <c r="I48" s="3">
         <v>6000</v>
@@ -4346,61 +4454,61 @@
         <v>6000</v>
       </c>
       <c r="K48" s="3">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="L48" s="3">
         <v>5500</v>
       </c>
       <c r="M48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="N48" s="3">
         <v>5600</v>
-      </c>
-      <c r="N48" s="3">
-        <v>5300</v>
       </c>
       <c r="O48" s="3">
         <v>5300</v>
       </c>
       <c r="P48" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="Q48" s="3">
         <v>5600</v>
       </c>
       <c r="R48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="S48" s="3">
         <v>5500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3500</v>
-      </c>
-      <c r="U48" s="3">
-        <v>3400</v>
       </c>
       <c r="V48" s="3">
         <v>3400</v>
       </c>
       <c r="W48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="X48" s="3">
         <v>3100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3200</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>3100</v>
       </c>
       <c r="Z48" s="3">
         <v>3100</v>
       </c>
       <c r="AA48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB48" s="3">
         <v>3200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3300</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>3500</v>
       </c>
       <c r="AD48" s="3">
         <v>3500</v>
@@ -4409,19 +4517,22 @@
         <v>3500</v>
       </c>
       <c r="AF48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AG48" s="3">
         <v>3400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4429,16 +4540,16 @@
         <v>300</v>
       </c>
       <c r="E49" s="3">
+        <v>300</v>
+      </c>
+      <c r="F49" s="3">
         <v>200</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>100</v>
@@ -4450,7 +4561,7 @@
         <v>100</v>
       </c>
       <c r="L49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M49" s="3">
         <v>200</v>
@@ -4462,7 +4573,7 @@
         <v>200</v>
       </c>
       <c r="P49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q49" s="3">
         <v>300</v>
@@ -4480,7 +4591,7 @@
         <v>300</v>
       </c>
       <c r="V49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="W49" s="3">
         <v>400</v>
@@ -4492,7 +4603,7 @@
         <v>400</v>
       </c>
       <c r="Z49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA49" s="3">
         <v>500</v>
@@ -4501,7 +4612,7 @@
         <v>500</v>
       </c>
       <c r="AC49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD49" s="3">
         <v>600</v>
@@ -4519,10 +4630,13 @@
         <v>600</v>
       </c>
       <c r="AI49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,31 +4840,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E54" s="3">
         <v>13100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>20700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>14600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>21000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>24700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,88 +5230,89 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>3300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3000</v>
       </c>
       <c r="J57" s="3">
         <v>3000</v>
       </c>
       <c r="K57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1500</v>
       </c>
       <c r="R57" s="3">
         <v>1500</v>
       </c>
       <c r="S57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>400</v>
       </c>
       <c r="AD57" s="3">
         <v>400</v>
@@ -5193,420 +5324,435 @@
         <v>400</v>
       </c>
       <c r="AG57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
         <v>1300</v>
       </c>
       <c r="F58" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>900</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1000</v>
       </c>
       <c r="R58" s="3">
         <v>1000</v>
       </c>
       <c r="S58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T58" s="3">
         <v>900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>600</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>500</v>
       </c>
       <c r="AB58" s="3">
         <v>500</v>
       </c>
       <c r="AC58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD58" s="3">
         <v>700</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>600</v>
       </c>
       <c r="AE58" s="3">
         <v>600</v>
       </c>
       <c r="AF58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG58" s="3">
         <v>300</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>200</v>
       </c>
       <c r="AH58" s="3">
         <v>200</v>
       </c>
       <c r="AI58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>26500</v>
+        <v>23100</v>
       </c>
       <c r="E59" s="3">
-        <v>26700</v>
+        <v>23100</v>
       </c>
       <c r="F59" s="3">
-        <v>27300</v>
+        <v>23200</v>
       </c>
       <c r="G59" s="3">
+        <v>23200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K59" s="3">
         <v>13200</v>
       </c>
-      <c r="H59" s="3">
-        <v>14000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>13000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>13200</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2500</v>
-      </c>
-      <c r="U59" s="3">
-        <v>2400</v>
       </c>
       <c r="V59" s="3">
         <v>2400</v>
       </c>
       <c r="W59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X59" s="3">
         <v>2000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1400</v>
       </c>
       <c r="Y59" s="3">
         <v>1400</v>
       </c>
       <c r="Z59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA59" s="3">
         <v>900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E60" s="3">
         <v>31000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AH60" s="3">
-        <v>2000</v>
       </c>
       <c r="AI60" s="3">
         <v>2000</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>2000</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4600</v>
       </c>
-      <c r="E61" s="3">
-        <v>4200</v>
-      </c>
       <c r="F61" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G61" s="3">
         <v>4400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K61" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="R61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V61" s="3">
         <v>2900</v>
       </c>
-      <c r="H61" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I61" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>3600</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="W61" s="3">
         <v>3100</v>
       </c>
-      <c r="L61" s="3">
-        <v>2400</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="X61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Z61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="AA61" s="3">
         <v>3000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2800</v>
-      </c>
-      <c r="P61" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R61" s="3">
-        <v>3500</v>
-      </c>
-      <c r="S61" s="3">
-        <v>2700</v>
-      </c>
-      <c r="T61" s="3">
-        <v>2800</v>
-      </c>
-      <c r="U61" s="3">
-        <v>2900</v>
-      </c>
-      <c r="V61" s="3">
-        <v>3100</v>
-      </c>
-      <c r="W61" s="3">
-        <v>2600</v>
-      </c>
-      <c r="X61" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>2900</v>
       </c>
       <c r="AB61" s="3">
         <v>2900</v>
       </c>
       <c r="AC61" s="3">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="AD61" s="3">
         <v>2400</v>
       </c>
       <c r="AE61" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="AF61" s="3">
         <v>2100</v>
       </c>
       <c r="AG61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AH61" s="3">
         <v>1800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5620,10 +5766,10 @@
         <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H62" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
         <v>400</v>
@@ -5635,28 +5781,28 @@
         <v>400</v>
       </c>
       <c r="L62" s="3">
+        <v>400</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>200</v>
-      </c>
-      <c r="S62" s="3">
-        <v>100</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -5676,8 +5822,8 @@
       <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
+      <c r="Z62" s="3">
+        <v>100</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
@@ -5688,8 +5834,8 @@
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>34900</v>
+        <v>35300</v>
       </c>
       <c r="E66" s="3">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="F66" s="3">
-        <v>35800</v>
+        <v>36100</v>
       </c>
       <c r="G66" s="3">
-        <v>20100</v>
+        <v>36700</v>
       </c>
       <c r="H66" s="3">
-        <v>21700</v>
+        <v>20900</v>
       </c>
       <c r="I66" s="3">
-        <v>20400</v>
+        <v>22400</v>
       </c>
       <c r="J66" s="3">
+        <v>21000</v>
+      </c>
+      <c r="K66" s="3">
         <v>20900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-223800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-217900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-210900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-202600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-193900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-185500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-176000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-167300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-160000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-152300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-144600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-137000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-129000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-121800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-116300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-110200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-105000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-95700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-89800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-86300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-82100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-77900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-69400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-55700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-51700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-40900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-21800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-15600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-7800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-2300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-2600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>31200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>21200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,176 +7346,182 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7700</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-7600</v>
       </c>
       <c r="M81" s="3">
         <v>-7600</v>
       </c>
       <c r="N81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="O81" s="3">
         <v>-8000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-4200</v>
       </c>
       <c r="X81" s="3">
         <v>-4200</v>
@@ -7335,37 +7530,40 @@
         <v>-4200</v>
       </c>
       <c r="Z81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7425,7 +7624,7 @@
         <v>300</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -7461,10 +7660,10 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -7488,7 +7687,7 @@
         <v>200</v>
       </c>
       <c r="AE83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF83" s="3">
         <v>100</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>100</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-2800</v>
       </c>
       <c r="AF89" s="3">
         <v>-2800</v>
       </c>
       <c r="AG89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,19 +8365,20 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
@@ -8166,19 +8387,19 @@
         <v>-300</v>
       </c>
       <c r="I91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -8187,28 +8408,28 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-300</v>
       </c>
       <c r="U91" s="3">
         <v>-300</v>
       </c>
       <c r="V91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>-100</v>
@@ -8235,19 +8456,22 @@
         <v>-100</v>
       </c>
       <c r="AF91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,19 +8675,22 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-300</v>
       </c>
       <c r="G94" s="3">
         <v>-300</v>
@@ -8469,19 +8699,19 @@
         <v>-300</v>
       </c>
       <c r="I94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-100</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
@@ -8490,28 +8720,28 @@
         <v>-100</v>
       </c>
       <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>-300</v>
       </c>
       <c r="V94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-100</v>
       </c>
       <c r="X94" s="3">
         <v>-100</v>
@@ -8538,19 +8768,22 @@
         <v>-100</v>
       </c>
       <c r="AF94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,190 +9233,196 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>20200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>14100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>7700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>11900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -9181,116 +9430,122 @@
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>VNRX</t>
   </si>
@@ -656,169 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>200</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
@@ -827,26 +834,26 @@
         <v>200</v>
       </c>
       <c r="J8" s="3">
+        <v>200</v>
+      </c>
+      <c r="K8" s="3">
+        <v>200</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -907,8 +914,14 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1011,22 +1024,28 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
@@ -1035,14 +1054,14 @@
         <v>200</v>
       </c>
       <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
+        <v>200</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1115,8 +1134,14 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1178,120 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F12" s="3">
         <v>3500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>4600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>4500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>4700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>3600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>3400</v>
-      </c>
-      <c r="P12" s="3">
-        <v>4200</v>
       </c>
       <c r="Q12" s="3">
         <v>3400</v>
       </c>
       <c r="R12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="S12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T12" s="3">
         <v>3600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>3000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>3200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>3700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>2600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>2300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>2300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>2900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>2500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>2300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>2400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>2100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,37 +1394,43 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1447,26 +1486,32 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>4</v>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1504,13 +1549,13 @@
         <v>300</v>
       </c>
       <c r="O15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P15" s="3">
         <v>300</v>
       </c>
       <c r="Q15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R15" s="3">
         <v>300</v>
@@ -1519,7 +1564,7 @@
         <v>300</v>
       </c>
       <c r="T15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U15" s="3">
         <v>300</v>
@@ -1534,7 +1579,7 @@
         <v>200</v>
       </c>
       <c r="Y15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z15" s="3">
         <v>200</v>
@@ -1551,26 +1596,32 @@
       <c r="AD15" s="3">
         <v>200</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
+      <c r="AE15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>200</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>8100</v>
-      </c>
-      <c r="L17" s="3">
-        <v>8000</v>
       </c>
       <c r="M17" s="3">
         <v>8100</v>
       </c>
       <c r="N17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="P17" s="3">
         <v>7800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>8800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>4600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>4000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>3900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>3300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-7000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-8700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-8700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-9500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-8100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-7700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-8800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-6100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-4500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-5900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1915,10 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1862,55 +1929,55 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>200</v>
@@ -1919,17 +1986,17 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1949,117 +2016,129 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="G21" s="3">
         <v>-6700</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-8500</v>
       </c>
       <c r="H21" s="3">
         <v>-8100</v>
       </c>
       <c r="I21" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-9200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-8600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-7000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-7500</v>
       </c>
       <c r="N21" s="3">
         <v>-7500</v>
       </c>
       <c r="O21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-7800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-5300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-4900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-4100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-4800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-5600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-3900</v>
       </c>
       <c r="Z21" s="3">
         <v>-4000</v>
       </c>
       <c r="AA21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2088,10 +2167,10 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2159,115 +2238,127 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="G23" s="3">
         <v>-7100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-8800</v>
       </c>
       <c r="H23" s="3">
         <v>-8500</v>
       </c>
       <c r="I23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-9600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-8900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-7300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-7700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-8100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-6100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-5900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z23" s="3">
         <v>-4200</v>
       </c>
       <c r="AA23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,11 +2383,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2370,8 +2461,14 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="G26" s="3">
         <v>-7100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-8800</v>
       </c>
       <c r="H26" s="3">
         <v>-8500</v>
       </c>
       <c r="I26" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-9600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-8900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-7700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-8100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-5200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-5900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z26" s="3">
         <v>-4200</v>
       </c>
       <c r="AA26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G27" s="3">
         <v>-7000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-8700</v>
       </c>
       <c r="H27" s="3">
         <v>-8400</v>
       </c>
       <c r="I27" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-8800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-7600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-8000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-6100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-5800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z27" s="3">
         <v>-4200</v>
       </c>
       <c r="AA27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3231,14 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3110,55 +3249,55 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-200</v>
@@ -3167,17 +3306,17 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3197,117 +3336,129 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G33" s="3">
         <v>-7000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-8700</v>
       </c>
       <c r="H33" s="3">
         <v>-8400</v>
       </c>
       <c r="I33" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-8800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-7200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-7600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-7600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-8000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-6100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-5800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z33" s="3">
         <v>-4200</v>
       </c>
       <c r="AA33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G35" s="3">
         <v>-7000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-8700</v>
       </c>
       <c r="H35" s="3">
         <v>-8400</v>
       </c>
       <c r="I35" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-8800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-7200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-7600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-7600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-8000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-6100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-5800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z35" s="3">
         <v>-4200</v>
       </c>
       <c r="AA35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3870,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F41" s="3">
         <v>5400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>19700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>16400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>16700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>23700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>20600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>22900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>27900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>33100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>19400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>20900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>21300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>12000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>17000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>19700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>18500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>16200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>13400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>16400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>11900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>14300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>10100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>13800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>16500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>18500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,50 +4086,56 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>200</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3969,8 +4154,8 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3978,8 +4163,8 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
+      <c r="Z43" s="3">
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>4</v>
@@ -3993,11 +4178,11 @@
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
@@ -4011,8 +4196,14 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,11 +4228,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4115,19 +4306,25 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>500</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
@@ -4136,195 +4333,207 @@
         <v>500</v>
       </c>
       <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
+        <v>500</v>
+      </c>
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F46" s="3">
         <v>6800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>21500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>18600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>26000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>24400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>29400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>34700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>20300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>22200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>22400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>13100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>17600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>20300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>19200</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>17100</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>13900</v>
       </c>
       <c r="AB46" s="3">
         <v>17100</v>
       </c>
       <c r="AC46" s="3">
+        <v>13900</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>17100</v>
+      </c>
+      <c r="AE46" s="3">
         <v>12500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>14900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>10600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>14300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>17000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>19000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,11 +4558,11 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4427,112 +4636,124 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F48" s="3">
         <v>5500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6000</v>
       </c>
       <c r="K48" s="3">
         <v>6000</v>
       </c>
       <c r="L48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N48" s="3">
         <v>5500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3400</v>
-      </c>
-      <c r="X48" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>3200</v>
       </c>
       <c r="Z48" s="3">
         <v>3100</v>
       </c>
       <c r="AA48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AB48" s="3">
         <v>3100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD48" s="3">
         <v>3200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>3300</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>3500</v>
       </c>
       <c r="AF48" s="3">
         <v>3500</v>
       </c>
       <c r="AG48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AI48" s="3">
         <v>3400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>3000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4543,19 +4764,19 @@
         <v>300</v>
       </c>
       <c r="F49" s="3">
+        <v>300</v>
+      </c>
+      <c r="G49" s="3">
+        <v>300</v>
+      </c>
+      <c r="H49" s="3">
         <v>200</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -4564,10 +4785,10 @@
         <v>100</v>
       </c>
       <c r="M49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O49" s="3">
         <v>200</v>
@@ -4576,10 +4797,10 @@
         <v>200</v>
       </c>
       <c r="Q49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S49" s="3">
         <v>300</v>
@@ -4594,10 +4815,10 @@
         <v>300</v>
       </c>
       <c r="W49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y49" s="3">
         <v>400</v>
@@ -4606,19 +4827,19 @@
         <v>400</v>
       </c>
       <c r="AA49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AB49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC49" s="3">
         <v>500</v>
       </c>
       <c r="AD49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AE49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AF49" s="3">
         <v>600</v>
@@ -4633,10 +4854,16 @@
         <v>600</v>
       </c>
       <c r="AJ49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AL49" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +5076,14 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4869,11 +5108,11 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4947,8 +5186,14 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F54" s="3">
         <v>12700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>18000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>27600</v>
       </c>
       <c r="J54" s="3">
         <v>18000</v>
       </c>
       <c r="K54" s="3">
+        <v>27600</v>
+      </c>
+      <c r="L54" s="3">
+        <v>18000</v>
+      </c>
+      <c r="M54" s="3">
         <v>18300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>23300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>24300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>31700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>27500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>30000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>40500</v>
-      </c>
-      <c r="S54" s="3">
-        <v>26200</v>
-      </c>
-      <c r="T54" s="3">
-        <v>26100</v>
       </c>
       <c r="U54" s="3">
         <v>26200</v>
       </c>
       <c r="V54" s="3">
+        <v>26100</v>
+      </c>
+      <c r="W54" s="3">
+        <v>26200</v>
+      </c>
+      <c r="X54" s="3">
         <v>16900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>21300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>23800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>22900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>20600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>17500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>20700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>16300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>19000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>14600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>18400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>21000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>22500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,94 +5490,96 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>400</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>400</v>
       </c>
       <c r="AF57" s="3">
         <v>400</v>
@@ -5327,75 +5588,81 @@
         <v>400</v>
       </c>
       <c r="AH57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1500</v>
       </c>
       <c r="I58" s="3">
         <v>1500</v>
       </c>
       <c r="J58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L58" s="3">
         <v>1400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1100</v>
       </c>
       <c r="M58" s="3">
         <v>1200</v>
       </c>
       <c r="N58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P58" s="3">
         <v>1400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>800</v>
       </c>
       <c r="Q58" s="3">
         <v>900</v>
       </c>
       <c r="R58" s="3">
+        <v>800</v>
+      </c>
+      <c r="S58" s="3">
+        <v>900</v>
+      </c>
+      <c r="T58" s="3">
         <v>1000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
-      </c>
-      <c r="U58" s="3">
-        <v>800</v>
-      </c>
-      <c r="V58" s="3">
-        <v>700</v>
       </c>
       <c r="W58" s="3">
         <v>800</v>
@@ -5410,349 +5677,373 @@
         <v>700</v>
       </c>
       <c r="AA58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC58" s="3">
         <v>600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
         <v>23100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>23100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>23200</v>
       </c>
-      <c r="G59" s="3">
-        <v>23200</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
         <v>10200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>10400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>10000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>13200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>13600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>13900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>3600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1800</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>1400</v>
       </c>
       <c r="AI59" s="3">
         <v>1600</v>
       </c>
       <c r="AJ59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AL59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F60" s="3">
         <v>30300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>31000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>31500</v>
       </c>
-      <c r="G60" s="3">
-        <v>31800</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>8900</v>
+      </c>
+      <c r="J60" s="3">
         <v>17700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>17200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>17400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>17000</v>
       </c>
       <c r="M60" s="3">
         <v>17400</v>
       </c>
       <c r="N60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="O60" s="3">
+        <v>17400</v>
+      </c>
+      <c r="P60" s="3">
         <v>17500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>6200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3500</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>2300</v>
       </c>
       <c r="AB60" s="3">
         <v>2700</v>
       </c>
       <c r="AC60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE60" s="3">
         <v>3300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>2200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>2300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G61" s="3">
         <v>4600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2400</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O61" s="3">
-        <v>3000</v>
       </c>
       <c r="P61" s="3">
         <v>2800</v>
       </c>
       <c r="Q61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S61" s="3">
         <v>3100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>3000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5784,16 +6075,16 @@
         <v>400</v>
       </c>
       <c r="M62" s="3">
+        <v>400</v>
+      </c>
+      <c r="N62" s="3">
+        <v>400</v>
+      </c>
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
-      </c>
-      <c r="O62" s="3">
-        <v>200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
       </c>
       <c r="Q62" s="3">
         <v>200</v>
@@ -5808,7 +6099,7 @@
         <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
@@ -5825,11 +6116,11 @@
       <c r="Z62" s="3">
         <v>100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
+      <c r="AA62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>100</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
@@ -5837,11 +6128,11 @@
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -5855,8 +6146,14 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="F66" s="3">
         <v>35300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>36000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>36100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>36700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>20900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>22400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>21000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>20900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>20000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>19900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>20600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>8700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>7100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>7600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>7700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>7100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>6500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>5300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>5600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>6200</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>4700</v>
       </c>
       <c r="AF66" s="3">
         <v>5000</v>
       </c>
       <c r="AG66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AH66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AI66" s="3">
         <v>4400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>4000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-235000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-229500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-223800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-217900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-210900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-202600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-193900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-185500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-176000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-167300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-160000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-152300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-144600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-137000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-121800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-116300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-110200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-105000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-100700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-95700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-89800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-86300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-82100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-77900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-69400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-55700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-51700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-40900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F76" s="3">
         <v>-21500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-21800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-15600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-7800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-2000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-2300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-2600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>17900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>21300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>26700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>31200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>16300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>19000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>18700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>9200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>17800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>16400</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>15100</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>12100</v>
       </c>
       <c r="AB76" s="3">
         <v>15100</v>
       </c>
       <c r="AC76" s="3">
-        <v>10000</v>
+        <v>12100</v>
       </c>
       <c r="AD76" s="3">
-        <v>14000</v>
+        <v>15100</v>
       </c>
       <c r="AE76" s="3">
         <v>10000</v>
       </c>
       <c r="AF76" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AH76" s="3">
         <v>13400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>16600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>18500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G81" s="3">
         <v>-7000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-8700</v>
       </c>
       <c r="H81" s="3">
         <v>-8400</v>
       </c>
       <c r="I81" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-8800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-7200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-7600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-7600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-8000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-6100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-5800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z81" s="3">
         <v>-4200</v>
       </c>
       <c r="AA81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7995,10 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7627,10 +8024,10 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -7663,13 +8060,13 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
       </c>
       <c r="Y83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -7690,10 +8087,10 @@
         <v>200</v>
       </c>
       <c r="AF83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH83" s="3">
         <v>100</v>
@@ -7704,8 +8101,14 @@
       <c r="AJ83" s="3">
         <v>100</v>
       </c>
+      <c r="AK83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="G89" s="3">
         <v>-6700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-8300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-7300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-6200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-6200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-4400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-4800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-2800</v>
       </c>
       <c r="Z89" s="3">
         <v>-3700</v>
       </c>
       <c r="AA89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,76 +8805,78 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-300</v>
       </c>
       <c r="J91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
@@ -8459,19 +8900,25 @@
         <v>-100</v>
       </c>
       <c r="AG91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,13 +9131,19 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
@@ -8693,61 +9152,61 @@
         <v>-100</v>
       </c>
       <c r="G94" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="H94" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>-300</v>
       </c>
       <c r="J94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
       </c>
       <c r="Z94" s="3">
         <v>-100</v>
@@ -8771,19 +9230,25 @@
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9285,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,11 +9313,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,189 +9721,201 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F100" s="3">
         <v>5600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>17300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>8100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>6700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>20200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>4600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>14100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>4600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>5200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>6600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>9100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>7700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>200</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>300</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>1100</v>
       </c>
       <c r="AH100" s="3">
         <v>300</v>
       </c>
       <c r="AI100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK100" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>200</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
       </c>
       <c r="AC101" s="3">
         <v>200</v>
@@ -9427,125 +9924,137 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-5800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-9000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>9900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>3200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-5100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>13600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>9300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>2300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>2700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>4500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>4100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>VNRX</t>
   </si>
@@ -656,179 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3">
         <v>200</v>
       </c>
       <c r="F8" s="3">
+        <v>200</v>
+      </c>
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>200</v>
       </c>
       <c r="I8" s="3">
         <v>200</v>
@@ -840,23 +844,23 @@
         <v>200</v>
       </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -920,8 +924,11 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1030,25 +1037,28 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
+        <v>200</v>
+      </c>
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>200</v>
@@ -1060,11 +1070,11 @@
         <v>200</v>
       </c>
       <c r="L10" s="3">
+        <v>200</v>
+      </c>
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="E12" s="3">
         <v>2600</v>
       </c>
       <c r="F12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G12" s="3">
         <v>3500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>3400</v>
       </c>
       <c r="Q12" s="3">
         <v>3400</v>
       </c>
       <c r="R12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S12" s="3">
         <v>4200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>2300</v>
       </c>
       <c r="AB12" s="3">
         <v>2300</v>
       </c>
       <c r="AC12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AD12" s="3">
         <v>2900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,16 +1417,19 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1417,23 +1437,23 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1492,8 +1512,8 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>4</v>
@@ -1501,8 +1521,8 @@
       <c r="AI14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1555,10 +1578,10 @@
         <v>300</v>
       </c>
       <c r="Q15" s="3">
+        <v>300</v>
+      </c>
+      <c r="R15" s="3">
         <v>200</v>
-      </c>
-      <c r="R15" s="3">
-        <v>300</v>
       </c>
       <c r="S15" s="3">
         <v>300</v>
@@ -1570,19 +1593,19 @@
         <v>300</v>
       </c>
       <c r="V15" s="3">
+        <v>300</v>
+      </c>
+      <c r="W15" s="3">
         <v>200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>300</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>200</v>
       </c>
       <c r="AA15" s="3">
         <v>200</v>
@@ -1602,8 +1625,8 @@
       <c r="AF15" s="3">
         <v>200</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
+      <c r="AG15" s="3">
+        <v>200</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>4</v>
@@ -1611,8 +1634,8 @@
       <c r="AI15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
+      <c r="AJ15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E17" s="3">
         <v>5800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3700</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>4200</v>
       </c>
       <c r="AA17" s="3">
         <v>4200</v>
       </c>
       <c r="AB17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AC17" s="3">
         <v>4000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4400</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>4600</v>
       </c>
       <c r="AF17" s="3">
         <v>4600</v>
       </c>
       <c r="AG17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AH17" s="3">
         <v>4000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AK17" s="3">
-        <v>3500</v>
       </c>
       <c r="AL17" s="3">
         <v>3500</v>
       </c>
+      <c r="AM17" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-8700</v>
       </c>
       <c r="J18" s="3">
         <v>-8700</v>
       </c>
       <c r="K18" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="L18" s="3">
         <v>-9500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-8000</v>
       </c>
       <c r="N18" s="3">
         <v>-8000</v>
       </c>
       <c r="O18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="P18" s="3">
         <v>-8100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3700</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA18" s="3">
         <v>-4200</v>
       </c>
       <c r="AB18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-4600</v>
       </c>
       <c r="AF18" s="3">
         <v>-4600</v>
       </c>
       <c r="AG18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>-3500</v>
       </c>
       <c r="AL18" s="3">
         <v>-3500</v>
       </c>
+      <c r="AM18" s="3">
+        <v>-3500</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,23 +1950,24 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1941,65 +1975,65 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>700</v>
-      </c>
-      <c r="R20" s="3">
-        <v>400</v>
       </c>
       <c r="S20" s="3">
         <v>400</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>500</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
       </c>
       <c r="W20" s="3">
         <v>200</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -2022,48 +2056,51 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5100</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-5500</v>
       </c>
       <c r="F21" s="3">
         <v>-5500</v>
       </c>
       <c r="G21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="H21" s="3">
         <v>-6700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-7500</v>
       </c>
       <c r="O21" s="3">
         <v>-7500</v>
@@ -2072,73 +2109,76 @@
         <v>-7500</v>
       </c>
       <c r="Q21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="R21" s="3">
         <v>-7800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2173,7 +2213,7 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -2244,82 +2284,85 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
-      <c r="AL22" s="3" t="s">
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-5900</v>
       </c>
       <c r="F23" s="3">
         <v>-5900</v>
       </c>
       <c r="G23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="H23" s="3">
         <v>-7100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-7700</v>
       </c>
       <c r="P23" s="3">
         <v>-7700</v>
       </c>
       <c r="Q23" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="R23" s="3">
         <v>-8100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA23" s="3">
         <v>-4200</v>
@@ -2328,37 +2371,40 @@
         <v>-4200</v>
       </c>
       <c r="AC23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,8 +2435,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,79 +2626,82 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-5900</v>
       </c>
       <c r="F26" s="3">
         <v>-5900</v>
       </c>
       <c r="G26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="H26" s="3">
         <v>-7100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-7700</v>
       </c>
       <c r="P26" s="3">
         <v>-7700</v>
       </c>
       <c r="Q26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="R26" s="3">
         <v>-8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3600</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA26" s="3">
         <v>-4200</v>
@@ -2658,108 +2710,111 @@
         <v>-4200</v>
       </c>
       <c r="AC26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-5800</v>
       </c>
       <c r="F27" s="3">
         <v>-5800</v>
       </c>
       <c r="G27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H27" s="3">
         <v>-7000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7700</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-7600</v>
       </c>
       <c r="P27" s="3">
         <v>-7600</v>
       </c>
       <c r="Q27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="R27" s="3">
         <v>-8000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA27" s="3">
         <v>-4200</v>
@@ -2768,37 +2823,40 @@
         <v>-4200</v>
       </c>
       <c r="AC27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,23 +3304,26 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -3261,65 +3331,65 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-700</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-400</v>
       </c>
       <c r="S32" s="3">
         <v>-400</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-500</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
       </c>
       <c r="W32" s="3">
         <v>-200</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3342,84 +3412,87 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-5800</v>
       </c>
       <c r="F33" s="3">
         <v>-5800</v>
       </c>
       <c r="G33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H33" s="3">
         <v>-7000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7700</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-7600</v>
       </c>
       <c r="P33" s="3">
         <v>-7600</v>
       </c>
       <c r="Q33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="R33" s="3">
         <v>-8000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA33" s="3">
         <v>-4200</v>
@@ -3428,37 +3501,40 @@
         <v>-4200</v>
       </c>
       <c r="AC33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,79 +3643,82 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-5800</v>
       </c>
       <c r="F35" s="3">
         <v>-5800</v>
       </c>
       <c r="G35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H35" s="3">
         <v>-7000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7700</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-7600</v>
       </c>
       <c r="P35" s="3">
         <v>-7600</v>
       </c>
       <c r="Q35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="R35" s="3">
         <v>-8000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA35" s="3">
         <v>-4200</v>
@@ -3648,152 +3727,158 @@
         <v>-4200</v>
       </c>
       <c r="AC35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>33100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>18500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>18500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>21700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,8 +4182,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4101,44 +4194,44 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
-      </c>
-      <c r="L43" s="3">
-        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4160,14 +4253,14 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>4</v>
@@ -4184,8 +4277,8 @@
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH43" s="3">
         <v>0</v>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4324,106 +4423,109 @@
         <v>300</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
       <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
       </c>
       <c r="K45" s="3">
         <v>500</v>
       </c>
       <c r="L45" s="3">
+        <v>500</v>
+      </c>
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
-      </c>
-      <c r="R45" s="3">
-        <v>1500</v>
       </c>
       <c r="S45" s="3">
         <v>1500</v>
       </c>
       <c r="T45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U45" s="3">
         <v>1600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1200</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1100</v>
       </c>
       <c r="X45" s="3">
         <v>1100</v>
       </c>
       <c r="Y45" s="3">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="Z45" s="3">
         <v>600</v>
       </c>
       <c r="AA45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>700</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>600</v>
       </c>
       <c r="AF45" s="3">
         <v>600</v>
       </c>
       <c r="AG45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH45" s="3">
         <v>500</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>400</v>
       </c>
       <c r="AI45" s="3">
         <v>400</v>
       </c>
       <c r="AJ45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK45" s="3">
         <v>500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4431,109 +4533,112 @@
         <v>3300</v>
       </c>
       <c r="E46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F46" s="3">
         <v>4100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>22200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>22400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>20300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>19000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>22000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4642,34 +4747,37 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5800</v>
-      </c>
-      <c r="K48" s="3">
-        <v>6000</v>
       </c>
       <c r="L48" s="3">
         <v>6000</v>
@@ -4678,61 +4786,61 @@
         <v>6000</v>
       </c>
       <c r="N48" s="3">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="O48" s="3">
         <v>5500</v>
       </c>
       <c r="P48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Q48" s="3">
         <v>5600</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>5300</v>
       </c>
       <c r="R48" s="3">
         <v>5300</v>
       </c>
       <c r="S48" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="T48" s="3">
         <v>5600</v>
       </c>
       <c r="U48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="V48" s="3">
         <v>5500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>3400</v>
       </c>
       <c r="Y48" s="3">
         <v>3400</v>
       </c>
       <c r="Z48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AA48" s="3">
         <v>3100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>3100</v>
       </c>
       <c r="AC48" s="3">
         <v>3100</v>
       </c>
       <c r="AD48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AE48" s="3">
         <v>3200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3300</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>3500</v>
       </c>
       <c r="AG48" s="3">
         <v>3500</v>
@@ -4741,19 +4849,22 @@
         <v>3500</v>
       </c>
       <c r="AI48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4770,16 +4881,16 @@
         <v>300</v>
       </c>
       <c r="H49" s="3">
+        <v>300</v>
+      </c>
+      <c r="I49" s="3">
         <v>200</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>100</v>
@@ -4791,7 +4902,7 @@
         <v>100</v>
       </c>
       <c r="O49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P49" s="3">
         <v>200</v>
@@ -4803,7 +4914,7 @@
         <v>200</v>
       </c>
       <c r="S49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T49" s="3">
         <v>300</v>
@@ -4821,7 +4932,7 @@
         <v>300</v>
       </c>
       <c r="Y49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z49" s="3">
         <v>400</v>
@@ -4833,7 +4944,7 @@
         <v>400</v>
       </c>
       <c r="AC49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD49" s="3">
         <v>500</v>
@@ -4842,7 +4953,7 @@
         <v>500</v>
       </c>
       <c r="AF49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AG49" s="3">
         <v>600</v>
@@ -4860,10 +4971,13 @@
         <v>600</v>
       </c>
       <c r="AL49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AM49" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5114,8 +5234,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E54" s="3">
         <v>8500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>40500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>22500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>24700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,97 +5622,98 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>3000</v>
       </c>
       <c r="M57" s="3">
         <v>3000</v>
       </c>
       <c r="N57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O57" s="3">
         <v>2500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1500</v>
       </c>
       <c r="U57" s="3">
         <v>1500</v>
       </c>
       <c r="V57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>400</v>
       </c>
       <c r="AG57" s="3">
         <v>400</v>
@@ -5594,36 +5725,39 @@
         <v>400</v>
       </c>
       <c r="AJ57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK57" s="3">
         <v>600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="E58" s="3">
         <v>1100</v>
       </c>
       <c r="F58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1500</v>
       </c>
       <c r="J58" s="3">
         <v>1500</v>
@@ -5632,418 +5766,430 @@
         <v>1500</v>
       </c>
       <c r="L58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>900</v>
-      </c>
-      <c r="T58" s="3">
-        <v>1000</v>
       </c>
       <c r="U58" s="3">
         <v>1000</v>
       </c>
       <c r="V58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>600</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>500</v>
       </c>
       <c r="AE58" s="3">
         <v>500</v>
       </c>
       <c r="AF58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG58" s="3">
         <v>700</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>600</v>
       </c>
       <c r="AH58" s="3">
         <v>600</v>
       </c>
       <c r="AI58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>300</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>200</v>
       </c>
       <c r="AK58" s="3">
         <v>200</v>
       </c>
       <c r="AL58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
         <v>400</v>
       </c>
       <c r="F59" s="3">
-        <v>23100</v>
+        <v>400</v>
       </c>
       <c r="G59" s="3">
         <v>23100</v>
       </c>
       <c r="H59" s="3">
+        <v>23100</v>
+      </c>
+      <c r="I59" s="3">
         <v>23200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2500</v>
-      </c>
-      <c r="X59" s="3">
-        <v>2400</v>
       </c>
       <c r="Y59" s="3">
         <v>2400</v>
       </c>
       <c r="Z59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA59" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>1400</v>
       </c>
       <c r="AB59" s="3">
         <v>1400</v>
       </c>
       <c r="AC59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD59" s="3">
         <v>900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E60" s="3">
         <v>8300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AK60" s="3">
-        <v>2000</v>
       </c>
       <c r="AL60" s="3">
         <v>2000</v>
       </c>
+      <c r="AM60" s="3">
+        <v>2000</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E61" s="3">
         <v>6200</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4700</v>
       </c>
       <c r="F61" s="3">
         <v>4700</v>
       </c>
       <c r="G61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H61" s="3">
         <v>4600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>2900</v>
       </c>
       <c r="AE61" s="3">
         <v>2900</v>
       </c>
       <c r="AF61" s="3">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="AG61" s="3">
         <v>2400</v>
       </c>
       <c r="AH61" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="AI61" s="3">
         <v>2100</v>
       </c>
       <c r="AJ61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AK61" s="3">
         <v>1800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6081,28 +6227,28 @@
         <v>400</v>
       </c>
       <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>200</v>
-      </c>
-      <c r="V62" s="3">
-        <v>100</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
@@ -6122,8 +6268,8 @@
       <c r="AB62" s="3">
         <v>100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
+      <c r="AC62" s="3">
+        <v>100</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
@@ -6134,8 +6280,8 @@
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E66" s="3">
         <v>37500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-241300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-235000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-229500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-223800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-217900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-210900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-202600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-193900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-185500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-176000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-167300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-160000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-152300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-144600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-137000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-129000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-121800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-116300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-110200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-105000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-100700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-95700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-89800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-86300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-82100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-77900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-69400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-55700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-51700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-40900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-27800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-24900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-21500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-21800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-15600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-7800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-2000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-2300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-2600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>21200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,194 +7921,200 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-5800</v>
       </c>
       <c r="F81" s="3">
         <v>-5800</v>
       </c>
       <c r="G81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H81" s="3">
         <v>-7000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7700</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-7600</v>
       </c>
       <c r="P81" s="3">
         <v>-7600</v>
       </c>
       <c r="Q81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="R81" s="3">
         <v>-8000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA81" s="3">
         <v>-4200</v>
@@ -7928,37 +8123,40 @@
         <v>-4200</v>
       </c>
       <c r="AC81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8030,7 +8229,7 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -8066,10 +8265,10 @@
         <v>200</v>
       </c>
       <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>100</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>200</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
@@ -8093,7 +8292,7 @@
         <v>200</v>
       </c>
       <c r="AH83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI83" s="3">
         <v>100</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>100</v>
       </c>
+      <c r="AM83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-5400</v>
       </c>
       <c r="F89" s="3">
         <v>-5400</v>
       </c>
       <c r="G89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="H89" s="3">
         <v>-6700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="AH89" s="3">
-        <v>-2800</v>
       </c>
       <c r="AI89" s="3">
         <v>-2800</v>
       </c>
       <c r="AJ89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AK89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,28 +9027,29 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-300</v>
@@ -8837,19 +9058,19 @@
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -8858,28 +9079,28 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-300</v>
       </c>
       <c r="X91" s="3">
         <v>-300</v>
       </c>
       <c r="Y91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
@@ -8906,19 +9127,22 @@
         <v>-100</v>
       </c>
       <c r="AI91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,28 +9364,31 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-300</v>
       </c>
       <c r="J94" s="3">
         <v>-300</v>
@@ -9167,19 +9397,19 @@
         <v>-300</v>
       </c>
       <c r="L94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>-100</v>
@@ -9188,28 +9418,28 @@
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>-300</v>
       </c>
       <c r="Y94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
@@ -9236,19 +9466,22 @@
         <v>-100</v>
       </c>
       <c r="AI94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,127 +9970,133 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E100" s="3">
         <v>3700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>20200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>14100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>6600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>9100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>7700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>11900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
@@ -9855,80 +10104,80 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>-100</v>
       </c>
       <c r="N101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -9936,125 +10185,131 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>9200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>VNRX</t>
   </si>
@@ -656,196 +656,203 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="3">
         <v>400</v>
       </c>
       <c r="F8" s="3">
+        <v>600</v>
+      </c>
+      <c r="G8" s="3">
+        <v>400</v>
+      </c>
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>200</v>
       </c>
       <c r="L8" s="3">
         <v>200</v>
@@ -854,26 +861,26 @@
         <v>200</v>
       </c>
       <c r="N8" s="3">
+        <v>200</v>
+      </c>
+      <c r="O8" s="3">
+        <v>200</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
@@ -934,13 +941,19 @@
       <c r="AN8" s="3">
         <v>0</v>
       </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>500</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
@@ -1050,34 +1063,40 @@
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E10" s="3">
         <v>400</v>
       </c>
       <c r="F10" s="3">
+        <v>600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>400</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>200</v>
@@ -1086,14 +1105,14 @@
         <v>200</v>
       </c>
       <c r="N10" s="3">
+        <v>200</v>
+      </c>
+      <c r="O10" s="3">
+        <v>200</v>
+      </c>
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1166,8 +1185,14 @@
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,124 +1233,132 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F12" s="3">
         <v>2300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>4700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>5500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>4900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>3100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>3400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>3400</v>
-      </c>
-      <c r="T12" s="3">
-        <v>4200</v>
       </c>
       <c r="U12" s="3">
         <v>3400</v>
       </c>
       <c r="V12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="W12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="X12" s="3">
         <v>3600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>3700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>3000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>3200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>3700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>2600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>2300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>2300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>2900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>2600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>2500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>2300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>2100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>1800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>1700</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>2700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,13 +1473,19 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>1000</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1457,32 +1496,32 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1538,26 +1577,32 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>4</v>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="3">
-        <v>0</v>
+      <c r="AL14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1565,10 +1610,10 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
@@ -1607,13 +1652,13 @@
         <v>300</v>
       </c>
       <c r="S15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T15" s="3">
         <v>300</v>
       </c>
       <c r="U15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V15" s="3">
         <v>300</v>
@@ -1622,7 +1667,7 @@
         <v>300</v>
       </c>
       <c r="X15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y15" s="3">
         <v>300</v>
@@ -1637,7 +1682,7 @@
         <v>200</v>
       </c>
       <c r="AC15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD15" s="3">
         <v>200</v>
@@ -1654,26 +1699,32 @@
       <c r="AH15" s="3">
         <v>200</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ15" s="3" t="s">
-        <v>4</v>
+      <c r="AI15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>200</v>
       </c>
       <c r="AK15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>0</v>
+      <c r="AL15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F17" s="3">
         <v>5700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>9800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>9200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>8100</v>
-      </c>
-      <c r="P17" s="3">
-        <v>8000</v>
       </c>
       <c r="Q17" s="3">
         <v>8100</v>
       </c>
       <c r="R17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="T17" s="3">
         <v>7800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>8800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>5700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>4000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>4300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>4400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>4600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>4600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>3900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>3400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>3300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>3500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-5900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-7000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-8700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-9000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-8000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-8100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-7700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-8800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-7600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-6100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-5700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,22 +2050,24 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
@@ -2009,55 +2076,55 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>200</v>
@@ -2066,17 +2133,17 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
@@ -2096,129 +2163,141 @@
         <v>0</v>
       </c>
       <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
         <v>500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-5100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-5500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-5500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-8500</v>
       </c>
       <c r="L21" s="3">
         <v>-8100</v>
       </c>
       <c r="M21" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="O21" s="3">
         <v>-9200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-8600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-7000</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-7500</v>
       </c>
       <c r="R21" s="3">
         <v>-7500</v>
       </c>
       <c r="S21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="U21" s="3">
         <v>-7800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-6900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-5300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-5900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-4900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-3900</v>
       </c>
       <c r="AD21" s="3">
         <v>-4000</v>
       </c>
       <c r="AE21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2226,7 +2305,7 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -2259,10 +2338,10 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2330,127 +2409,139 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5400</v>
+        <v>-6700</v>
       </c>
       <c r="E23" s="3">
         <v>-6300</v>
       </c>
       <c r="F23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="H23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-8800</v>
       </c>
       <c r="L23" s="3">
         <v>-8500</v>
       </c>
       <c r="M23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="O23" s="3">
         <v>-9600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-7700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-7700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-8100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-7200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-5200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD23" s="3">
         <v>-4200</v>
       </c>
       <c r="AE23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,11 +2578,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2565,8 +2656,14 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,129 +2778,141 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5400</v>
+        <v>-6700</v>
       </c>
       <c r="E26" s="3">
         <v>-6300</v>
       </c>
       <c r="F26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="H26" s="3">
         <v>-5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-8800</v>
       </c>
       <c r="L26" s="3">
         <v>-8500</v>
       </c>
       <c r="M26" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="O26" s="3">
         <v>-9600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-8900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-7300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-7700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-8100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-7200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-6100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-5200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD26" s="3">
         <v>-4200</v>
       </c>
       <c r="AE26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5400</v>
+        <v>-6700</v>
       </c>
       <c r="E27" s="3">
         <v>-6300</v>
@@ -2812,109 +2921,115 @@
         <v>-5400</v>
       </c>
       <c r="G27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-5800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-8700</v>
       </c>
       <c r="L27" s="3">
         <v>-8400</v>
       </c>
       <c r="M27" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-8800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-7200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-7600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-8000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-7100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-6100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-5100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD27" s="3">
         <v>-4200</v>
       </c>
       <c r="AE27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,22 +3510,28 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
@@ -3401,55 +3540,55 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>-200</v>
@@ -3458,17 +3597,17 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
@@ -3488,18 +3627,24 @@
         <v>0</v>
       </c>
       <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
         <v>-500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5400</v>
+        <v>-6700</v>
       </c>
       <c r="E33" s="3">
         <v>-6300</v>
@@ -3508,109 +3653,115 @@
         <v>-5400</v>
       </c>
       <c r="G33" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-8700</v>
       </c>
       <c r="L33" s="3">
         <v>-8400</v>
       </c>
       <c r="M33" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-8800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-7200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-7600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-7600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-8000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-7100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-6100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-5100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD33" s="3">
         <v>-4200</v>
       </c>
       <c r="AE33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,13 +3876,19 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5400</v>
+        <v>-6700</v>
       </c>
       <c r="E35" s="3">
         <v>-6300</v>
@@ -3740,230 +3897,242 @@
         <v>-5400</v>
       </c>
       <c r="G35" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-8700</v>
       </c>
       <c r="L35" s="3">
         <v>-8400</v>
       </c>
       <c r="M35" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-8800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-7200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-7600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-7600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-8000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-7100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-6100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-5100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD35" s="3">
         <v>-4200</v>
       </c>
       <c r="AE35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4217,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>20700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>19700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>16400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>16700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>23700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>20600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>22900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>27900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>33100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>19400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>20900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>21300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>12000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>17000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>19700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>18500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>16200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>13400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>16400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>11900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>14300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>13800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>16500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>18500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>21700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,8 +4457,14 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4287,53 +4472,53 @@
         <v>300</v>
       </c>
       <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>300</v>
+      </c>
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>200</v>
+      </c>
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
@@ -4352,8 +4537,8 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -4361,8 +4546,8 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
+      <c r="AD43" s="3">
+        <v>0</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
@@ -4376,11 +4561,11 @@
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="3">
-        <v>0</v>
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK43" s="3">
         <v>0</v>
@@ -4394,8 +4579,14 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,11 +4623,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4510,31 +4701,37 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>300</v>
       </c>
       <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>300</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
@@ -4543,207 +4740,219 @@
         <v>500</v>
       </c>
       <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
+        <v>500</v>
+      </c>
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>13500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>21900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>21500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>12200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>17700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>18600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>26000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>22000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>24400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>29400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>34700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>20300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>22200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>22400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>13100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>17600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>20300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>19200</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>17100</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>13900</v>
       </c>
       <c r="AF46" s="3">
         <v>17100</v>
       </c>
       <c r="AG46" s="3">
+        <v>13900</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>17100</v>
+      </c>
+      <c r="AI46" s="3">
         <v>12500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>14900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>10600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>14300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>17000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>19000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>22000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,11 +4989,11 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4858,124 +5067,136 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F48" s="3">
         <v>4800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5800</v>
-      </c>
-      <c r="M48" s="3">
-        <v>6000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>6000</v>
       </c>
       <c r="O48" s="3">
         <v>6000</v>
       </c>
       <c r="P48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R48" s="3">
         <v>5500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>3600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>3500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>3400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>3400</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>3200</v>
       </c>
       <c r="AD48" s="3">
         <v>3100</v>
       </c>
       <c r="AE48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AF48" s="3">
         <v>3100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AH48" s="3">
         <v>3200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>3300</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>3500</v>
       </c>
       <c r="AJ48" s="3">
         <v>3500</v>
       </c>
       <c r="AK48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AL48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AM48" s="3">
         <v>3400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>3000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>2100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4998,19 +5219,19 @@
         <v>300</v>
       </c>
       <c r="J49" s="3">
+        <v>300</v>
+      </c>
+      <c r="K49" s="3">
+        <v>300</v>
+      </c>
+      <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>100</v>
@@ -5019,10 +5240,10 @@
         <v>100</v>
       </c>
       <c r="Q49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S49" s="3">
         <v>200</v>
@@ -5031,10 +5252,10 @@
         <v>200</v>
       </c>
       <c r="U49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W49" s="3">
         <v>300</v>
@@ -5049,10 +5270,10 @@
         <v>300</v>
       </c>
       <c r="AA49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AB49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AC49" s="3">
         <v>400</v>
@@ -5061,19 +5282,19 @@
         <v>400</v>
       </c>
       <c r="AE49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AF49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AG49" s="3">
         <v>500</v>
       </c>
       <c r="AH49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AI49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AJ49" s="3">
         <v>600</v>
@@ -5088,10 +5309,16 @@
         <v>600</v>
       </c>
       <c r="AN49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AO49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AP49" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5555,14 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5360,11 +5599,11 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -5438,8 +5677,14 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F54" s="3">
         <v>6400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>28000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>18000</v>
-      </c>
-      <c r="M54" s="3">
-        <v>27600</v>
       </c>
       <c r="N54" s="3">
         <v>18000</v>
       </c>
       <c r="O54" s="3">
+        <v>27600</v>
+      </c>
+      <c r="P54" s="3">
+        <v>18000</v>
+      </c>
+      <c r="Q54" s="3">
         <v>18300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>23300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>24300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>31700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>27500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>30000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>35200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>40500</v>
-      </c>
-      <c r="W54" s="3">
-        <v>26200</v>
-      </c>
-      <c r="X54" s="3">
-        <v>26100</v>
       </c>
       <c r="Y54" s="3">
         <v>26200</v>
       </c>
       <c r="Z54" s="3">
+        <v>26100</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>26200</v>
+      </c>
+      <c r="AB54" s="3">
         <v>16900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>21300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>23800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>22900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>20600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>17500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>20700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>16300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>19000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>18400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>21000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>22500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>24700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,106 +6013,108 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>400</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>400</v>
       </c>
       <c r="AJ57" s="3">
         <v>400</v>
@@ -5862,87 +6123,93 @@
         <v>400</v>
       </c>
       <c r="AL57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AM57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AN57" s="3">
         <v>600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1500</v>
       </c>
       <c r="M58" s="3">
         <v>1500</v>
       </c>
       <c r="N58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P58" s="3">
         <v>1400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1100</v>
       </c>
       <c r="Q58" s="3">
         <v>1200</v>
       </c>
       <c r="R58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T58" s="3">
         <v>1400</v>
-      </c>
-      <c r="S58" s="3">
-        <v>900</v>
-      </c>
-      <c r="T58" s="3">
-        <v>800</v>
       </c>
       <c r="U58" s="3">
         <v>900</v>
       </c>
       <c r="V58" s="3">
+        <v>800</v>
+      </c>
+      <c r="W58" s="3">
+        <v>900</v>
+      </c>
+      <c r="X58" s="3">
         <v>1000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>900</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>800</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>700</v>
       </c>
       <c r="AA58" s="3">
         <v>800</v>
@@ -5957,393 +6224,417 @@
         <v>700</v>
       </c>
       <c r="AE58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG58" s="3">
         <v>600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>23100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>23100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>23200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>10200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>10400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>10000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>13200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>13400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>13600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>13900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>3800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>1800</v>
-      </c>
-      <c r="AK59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AL59" s="3">
-        <v>1400</v>
       </c>
       <c r="AM59" s="3">
         <v>1600</v>
       </c>
       <c r="AN59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AO59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AP59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F60" s="3">
         <v>11400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>8300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>30300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>31000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>31500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>8900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>17700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>17200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>17400</v>
-      </c>
-      <c r="P60" s="3">
-        <v>17000</v>
       </c>
       <c r="Q60" s="3">
         <v>17400</v>
       </c>
       <c r="R60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="S60" s="3">
+        <v>17400</v>
+      </c>
+      <c r="T60" s="3">
         <v>17500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>6500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>6000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>6200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>4300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>4700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>3200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>3500</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>2300</v>
       </c>
       <c r="AF60" s="3">
         <v>2700</v>
       </c>
       <c r="AG60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AI60" s="3">
         <v>3300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>2600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>2800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>2200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>2300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>2000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F61" s="3">
         <v>8500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2400</v>
-      </c>
-      <c r="R61" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S61" s="3">
-        <v>3000</v>
       </c>
       <c r="T61" s="3">
         <v>2800</v>
       </c>
       <c r="U61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W61" s="3">
         <v>3100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>3100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>3000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>2400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>2100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>2100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>1800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>1500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
@@ -6379,16 +6670,16 @@
         <v>400</v>
       </c>
       <c r="Q62" s="3">
+        <v>400</v>
+      </c>
+      <c r="R62" s="3">
+        <v>400</v>
+      </c>
+      <c r="S62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
-      </c>
-      <c r="S62" s="3">
-        <v>200</v>
-      </c>
-      <c r="T62" s="3">
-        <v>100</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
@@ -6403,7 +6694,7 @@
         <v>100</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
@@ -6420,11 +6711,11 @@
       <c r="AD62" s="3">
         <v>100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
+      <c r="AE62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>100</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
@@ -6432,11 +6723,11 @@
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="3">
-        <v>0</v>
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK62" s="3">
         <v>0</v>
@@ -6450,8 +6741,14 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,8 +7107,14 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6807,115 +7122,121 @@
         <v>42400</v>
       </c>
       <c r="E66" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>42400</v>
+      </c>
+      <c r="G66" s="3">
         <v>41800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>37500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>35500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>35300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>36000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>36100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>36700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>20900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>22400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>21000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>20900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>20000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>19900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>20600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>8700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>8500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>7100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>7600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>7700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>7100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>6000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>6500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>5500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>5300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>5600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>6200</v>
-      </c>
-      <c r="AH66" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>4700</v>
       </c>
       <c r="AJ66" s="3">
         <v>5000</v>
       </c>
       <c r="AK66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AL66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AM66" s="3">
         <v>4400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>4000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>3600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-259600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-252900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-246600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-241300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-235000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-229500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-223800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-217900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-210900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-202600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-193900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-185500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-176000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-167300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-160000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-152300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-144600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-137000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-129000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-121800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-116300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-110200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-105000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-100700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-95700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-89800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-86300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-82100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-77900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-69400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-55700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-51700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-40900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-34600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-31800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-27800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-24900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-21500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-21800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-15600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-7800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-2000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-2300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-2600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>11100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>17900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>21300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>26700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>31200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>16300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>19000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>18700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>9200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>14200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>17800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>16400</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>15100</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>12100</v>
       </c>
       <c r="AF76" s="3">
         <v>15100</v>
       </c>
       <c r="AG76" s="3">
-        <v>10000</v>
+        <v>12100</v>
       </c>
       <c r="AH76" s="3">
-        <v>14000</v>
+        <v>15100</v>
       </c>
       <c r="AI76" s="3">
         <v>10000</v>
       </c>
       <c r="AJ76" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AK76" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AL76" s="3">
         <v>13400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>16600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>18500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>21200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,134 +8493,146 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5400</v>
+        <v>-6700</v>
       </c>
       <c r="E81" s="3">
         <v>-6300</v>
@@ -8252,109 +8641,115 @@
         <v>-5400</v>
       </c>
       <c r="G81" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-8700</v>
       </c>
       <c r="L81" s="3">
         <v>-8400</v>
       </c>
       <c r="M81" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-8800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-7200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-7600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-7600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-8000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-7100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-6100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-5100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD81" s="3">
         <v>-4200</v>
       </c>
       <c r="AE81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8790,10 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8404,7 +8801,7 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
@@ -8434,10 +8831,10 @@
         <v>300</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -8470,13 +8867,13 @@
         <v>200</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
       </c>
       <c r="AC83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD83" s="3">
         <v>200</v>
@@ -8497,10 +8894,10 @@
         <v>200</v>
       </c>
       <c r="AJ83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AK83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL83" s="3">
         <v>100</v>
@@ -8511,8 +8908,14 @@
       <c r="AN83" s="3">
         <v>100</v>
       </c>
+      <c r="AO83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-8400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-8700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-5800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-6900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-4400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-6200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-2800</v>
       </c>
       <c r="AD89" s="3">
         <v>-3700</v>
       </c>
       <c r="AE89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9688,10 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9258,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -9267,70 +9708,70 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
       </c>
       <c r="U91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-100</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
@@ -9354,19 +9795,25 @@
         <v>-100</v>
       </c>
       <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,8 +10050,14 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9606,16 +10065,16 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-200</v>
-      </c>
       <c r="H94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <v>-200</v>
@@ -9624,61 +10083,61 @@
         <v>-100</v>
       </c>
       <c r="K94" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="L94" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="M94" s="3">
         <v>-300</v>
       </c>
       <c r="N94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>-100</v>
       </c>
       <c r="U94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-100</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
@@ -9702,19 +10161,25 @@
         <v>-100</v>
       </c>
       <c r="AK94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +10220,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,11 +10260,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9871,8 +10338,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,213 +10704,225 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>5600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>17300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>8100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>20200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>4600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>14100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>4600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>5200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>6600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>9100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>7700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>300</v>
-      </c>
-      <c r="AK100" s="3">
-        <v>1100</v>
       </c>
       <c r="AL100" s="3">
         <v>300</v>
       </c>
       <c r="AM100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AN100" s="3">
+        <v>300</v>
+      </c>
+      <c r="AO100" s="3">
         <v>11900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>200</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>0</v>
       </c>
       <c r="AG101" s="3">
         <v>200</v>
@@ -10434,137 +10931,149 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>100</v>
       </c>
-      <c r="AL101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
         <v>-100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-9000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>9900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-8900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-5500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-7000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>3200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-5100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>13600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>9300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>2700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>4500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>4100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>9200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-2000</v>
       </c>
     </row>
